--- a/astro-site/public/dl/kit-plan-financiero/01b-plan-financiero-previsional-5-anos.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/01b-plan-financiero-previsional-5-anos.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Año 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Año 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Año 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Año 4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Año 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Año 1'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Año 2'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Año 3'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Año 4'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Año 5'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Resumen'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,8 +30,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -145,46 +152,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -544,15 +551,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -560,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -567,6 +576,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -616,8 +626,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -626,25 +653,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -661,6 +688,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -784,7 +812,7 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -831,7 +859,7 @@
       </c>
       <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +906,7 @@
       </c>
       <c r="N8" s="10">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -925,7 +953,7 @@
       </c>
       <c r="N9" s="10">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -936,57 +964,58 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(D6:D9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="10">
         <f>SUM(E6:E9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F10" s="10">
         <f>SUM(F6:F9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="10">
         <f>SUM(G6:G9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I10" s="10">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="10">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K10" s="10">
         <f>SUM(K6:K9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L10" s="10">
         <f>SUM(L6:L9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M10" s="10">
         <f>SUM(M6:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N10" s="10">
         <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1038,7 +1067,7 @@
       </c>
       <c r="N13" s="10">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -1085,7 +1114,7 @@
       </c>
       <c r="N14" s="10">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -1132,7 +1161,7 @@
       </c>
       <c r="N15" s="10">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -1179,7 +1208,7 @@
       </c>
       <c r="N16" s="10">
         <f>SUM(B16:M16)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -1226,7 +1255,7 @@
       </c>
       <c r="N17" s="10">
         <f>SUM(B17:M17)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -1273,7 +1302,7 @@
       </c>
       <c r="N18" s="10">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -1284,57 +1313,58 @@
       </c>
       <c r="B19" s="10">
         <f>SUM(B13:B18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="10">
         <f>SUM(C13:C18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D13:D18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E13:E18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F13:F18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="10">
         <f>SUM(G13:G18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H13:H18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I19" s="10">
         <f>SUM(I13:I18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="10">
         <f>SUM(J13:J18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K19" s="10">
         <f>SUM(K13:K18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L19" s="10">
         <f>SUM(L13:L18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M19" s="10">
         <f>SUM(M13:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N19" s="10">
         <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -1343,55 +1373,55 @@
       </c>
       <c r="B21" s="13">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="13">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="13">
         <f>D10-D19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="13">
         <f>E10-E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F21" s="13">
         <f>F10-F19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="13">
         <f>G10-G19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H21" s="13">
         <f>H10-H19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I21" s="13">
         <f>I10-I19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J21" s="13">
         <f>J10-J19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K21" s="13">
         <f>K10-K19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L21" s="13">
         <f>L10-L19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M21" s="13">
         <f>M10-M19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13">
         <f>N10-N19</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -1402,57 +1432,58 @@
       </c>
       <c r="B22" s="14">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D22" s="14">
         <f>IF(D10=0,0,D21/D10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>IF(E10=0,0,E21/E10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>IF(F10=0,0,F21/F10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>IF(G10=0,0,G21/G10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H22" s="14">
         <f>IF(H10=0,0,H21/H10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I22" s="14">
         <f>IF(I10=0,0,I21/I10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J22" s="14">
         <f>IF(J10=0,0,J21/J10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K22" s="14">
         <f>IF(K10=0,0,K21/K10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L22" s="14">
         <f>IF(L10=0,0,L21/L10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M22" s="14">
         <f>IF(M10=0,0,M21/M10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N22" s="14">
         <f>IF(N10=0,0,N21/N10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -1466,7 +1497,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1475,25 +1515,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1510,6 +1550,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1633,7 +1674,7 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -1680,7 +1721,7 @@
       </c>
       <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -1727,7 +1768,7 @@
       </c>
       <c r="N8" s="10">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -1774,7 +1815,7 @@
       </c>
       <c r="N9" s="10">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -1785,57 +1826,58 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(D6:D9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="10">
         <f>SUM(E6:E9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F10" s="10">
         <f>SUM(F6:F9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="10">
         <f>SUM(G6:G9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I10" s="10">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="10">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K10" s="10">
         <f>SUM(K6:K9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L10" s="10">
         <f>SUM(L6:L9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M10" s="10">
         <f>SUM(M6:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N10" s="10">
         <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1887,7 +1929,7 @@
       </c>
       <c r="N13" s="10">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -1934,7 +1976,7 @@
       </c>
       <c r="N14" s="10">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -1981,7 +2023,7 @@
       </c>
       <c r="N15" s="10">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -2028,7 +2070,7 @@
       </c>
       <c r="N16" s="10">
         <f>SUM(B16:M16)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2075,7 +2117,7 @@
       </c>
       <c r="N17" s="10">
         <f>SUM(B17:M17)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -2122,7 +2164,7 @@
       </c>
       <c r="N18" s="10">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -2133,57 +2175,58 @@
       </c>
       <c r="B19" s="10">
         <f>SUM(B13:B18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="10">
         <f>SUM(C13:C18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D13:D18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E13:E18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F13:F18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="10">
         <f>SUM(G13:G18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H13:H18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I19" s="10">
         <f>SUM(I13:I18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="10">
         <f>SUM(J13:J18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K19" s="10">
         <f>SUM(K13:K18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L19" s="10">
         <f>SUM(L13:L18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M19" s="10">
         <f>SUM(M13:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N19" s="10">
         <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -2192,55 +2235,55 @@
       </c>
       <c r="B21" s="13">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="13">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="13">
         <f>D10-D19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="13">
         <f>E10-E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F21" s="13">
         <f>F10-F19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="13">
         <f>G10-G19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H21" s="13">
         <f>H10-H19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I21" s="13">
         <f>I10-I19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J21" s="13">
         <f>J10-J19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K21" s="13">
         <f>K10-K19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L21" s="13">
         <f>L10-L19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M21" s="13">
         <f>M10-M19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13">
         <f>N10-N19</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -2251,57 +2294,58 @@
       </c>
       <c r="B22" s="14">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D22" s="14">
         <f>IF(D10=0,0,D21/D10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>IF(E10=0,0,E21/E10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>IF(F10=0,0,F21/F10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>IF(G10=0,0,G21/G10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H22" s="14">
         <f>IF(H10=0,0,H21/H10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I22" s="14">
         <f>IF(I10=0,0,I21/I10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J22" s="14">
         <f>IF(J10=0,0,J21/J10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K22" s="14">
         <f>IF(K10=0,0,K21/K10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L22" s="14">
         <f>IF(L10=0,0,L21/L10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M22" s="14">
         <f>IF(M10=0,0,M21/M10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N22" s="14">
         <f>IF(N10=0,0,N21/N10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -2315,7 +2359,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2324,25 +2377,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2359,6 +2412,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2482,7 +2536,7 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2529,7 +2583,7 @@
       </c>
       <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -2576,7 +2630,7 @@
       </c>
       <c r="N8" s="10">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -2623,7 +2677,7 @@
       </c>
       <c r="N9" s="10">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2634,57 +2688,58 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(D6:D9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="10">
         <f>SUM(E6:E9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F10" s="10">
         <f>SUM(F6:F9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="10">
         <f>SUM(G6:G9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I10" s="10">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="10">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K10" s="10">
         <f>SUM(K6:K9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L10" s="10">
         <f>SUM(L6:L9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M10" s="10">
         <f>SUM(M6:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N10" s="10">
         <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -2736,7 +2791,7 @@
       </c>
       <c r="N13" s="10">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -2783,7 +2838,7 @@
       </c>
       <c r="N14" s="10">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -2830,7 +2885,7 @@
       </c>
       <c r="N15" s="10">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -2877,7 +2932,7 @@
       </c>
       <c r="N16" s="10">
         <f>SUM(B16:M16)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2924,7 +2979,7 @@
       </c>
       <c r="N17" s="10">
         <f>SUM(B17:M17)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -2971,7 +3026,7 @@
       </c>
       <c r="N18" s="10">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -2982,57 +3037,58 @@
       </c>
       <c r="B19" s="10">
         <f>SUM(B13:B18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="10">
         <f>SUM(C13:C18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D13:D18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E13:E18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F13:F18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="10">
         <f>SUM(G13:G18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H13:H18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I19" s="10">
         <f>SUM(I13:I18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="10">
         <f>SUM(J13:J18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K19" s="10">
         <f>SUM(K13:K18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L19" s="10">
         <f>SUM(L13:L18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M19" s="10">
         <f>SUM(M13:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N19" s="10">
         <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -3041,55 +3097,55 @@
       </c>
       <c r="B21" s="13">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="13">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="13">
         <f>D10-D19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="13">
         <f>E10-E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F21" s="13">
         <f>F10-F19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="13">
         <f>G10-G19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H21" s="13">
         <f>H10-H19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I21" s="13">
         <f>I10-I19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J21" s="13">
         <f>J10-J19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K21" s="13">
         <f>K10-K19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L21" s="13">
         <f>L10-L19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M21" s="13">
         <f>M10-M19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13">
         <f>N10-N19</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -3100,57 +3156,58 @@
       </c>
       <c r="B22" s="14">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D22" s="14">
         <f>IF(D10=0,0,D21/D10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>IF(E10=0,0,E21/E10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>IF(F10=0,0,F21/F10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>IF(G10=0,0,G21/G10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H22" s="14">
         <f>IF(H10=0,0,H21/H10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I22" s="14">
         <f>IF(I10=0,0,I21/I10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J22" s="14">
         <f>IF(J10=0,0,J21/J10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K22" s="14">
         <f>IF(K10=0,0,K21/K10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L22" s="14">
         <f>IF(L10=0,0,L21/L10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M22" s="14">
         <f>IF(M10=0,0,M21/M10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N22" s="14">
         <f>IF(N10=0,0,N21/N10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -3164,7 +3221,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3173,25 +3239,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3208,6 +3274,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3331,7 +3398,7 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -3378,7 +3445,7 @@
       </c>
       <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -3425,7 +3492,7 @@
       </c>
       <c r="N8" s="10">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -3472,7 +3539,7 @@
       </c>
       <c r="N9" s="10">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3483,57 +3550,58 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(D6:D9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="10">
         <f>SUM(E6:E9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F10" s="10">
         <f>SUM(F6:F9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="10">
         <f>SUM(G6:G9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I10" s="10">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="10">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K10" s="10">
         <f>SUM(K6:K9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L10" s="10">
         <f>SUM(L6:L9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M10" s="10">
         <f>SUM(M6:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N10" s="10">
         <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -3585,7 +3653,7 @@
       </c>
       <c r="N13" s="10">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3632,7 +3700,7 @@
       </c>
       <c r="N14" s="10">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -3679,7 +3747,7 @@
       </c>
       <c r="N15" s="10">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -3726,7 +3794,7 @@
       </c>
       <c r="N16" s="10">
         <f>SUM(B16:M16)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -3773,7 +3841,7 @@
       </c>
       <c r="N17" s="10">
         <f>SUM(B17:M17)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -3820,7 +3888,7 @@
       </c>
       <c r="N18" s="10">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -3831,57 +3899,58 @@
       </c>
       <c r="B19" s="10">
         <f>SUM(B13:B18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="10">
         <f>SUM(C13:C18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D13:D18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E13:E18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F13:F18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="10">
         <f>SUM(G13:G18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H13:H18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I19" s="10">
         <f>SUM(I13:I18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="10">
         <f>SUM(J13:J18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K19" s="10">
         <f>SUM(K13:K18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L19" s="10">
         <f>SUM(L13:L18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M19" s="10">
         <f>SUM(M13:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N19" s="10">
         <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -3890,55 +3959,55 @@
       </c>
       <c r="B21" s="13">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="13">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="13">
         <f>D10-D19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="13">
         <f>E10-E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F21" s="13">
         <f>F10-F19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="13">
         <f>G10-G19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H21" s="13">
         <f>H10-H19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I21" s="13">
         <f>I10-I19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J21" s="13">
         <f>J10-J19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K21" s="13">
         <f>K10-K19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L21" s="13">
         <f>L10-L19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M21" s="13">
         <f>M10-M19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13">
         <f>N10-N19</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -3949,57 +4018,58 @@
       </c>
       <c r="B22" s="14">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D22" s="14">
         <f>IF(D10=0,0,D21/D10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>IF(E10=0,0,E21/E10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>IF(F10=0,0,F21/F10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>IF(G10=0,0,G21/G10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H22" s="14">
         <f>IF(H10=0,0,H21/H10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I22" s="14">
         <f>IF(I10=0,0,I21/I10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J22" s="14">
         <f>IF(J10=0,0,J21/J10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K22" s="14">
         <f>IF(K10=0,0,K21/K10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L22" s="14">
         <f>IF(L10=0,0,L21/L10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M22" s="14">
         <f>IF(M10=0,0,M21/M10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N22" s="14">
         <f>IF(N10=0,0,N21/N10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -4013,7 +4083,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4022,25 +4101,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4057,6 +4136,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4180,7 +4260,7 @@
       </c>
       <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -4227,7 +4307,7 @@
       </c>
       <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -4274,7 +4354,7 @@
       </c>
       <c r="N8" s="10">
         <f>SUM(B8:M8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -4321,7 +4401,7 @@
       </c>
       <c r="N9" s="10">
         <f>SUM(B9:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -4332,57 +4412,58 @@
       </c>
       <c r="B10" s="10">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="10">
         <f>SUM(C6:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>SUM(D6:D9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="10">
         <f>SUM(E6:E9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F10" s="10">
         <f>SUM(F6:F9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="10">
         <f>SUM(G6:G9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H10" s="10">
         <f>SUM(H6:H9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I10" s="10">
         <f>SUM(I6:I9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J10" s="10">
         <f>SUM(J6:J9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K10" s="10">
         <f>SUM(K6:K9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L10" s="10">
         <f>SUM(L6:L9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M10" s="10">
         <f>SUM(M6:M9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N10" s="10">
         <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -4434,7 +4515,7 @@
       </c>
       <c r="N13" s="10">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -4481,7 +4562,7 @@
       </c>
       <c r="N14" s="10">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -4528,7 +4609,7 @@
       </c>
       <c r="N15" s="10">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -4575,7 +4656,7 @@
       </c>
       <c r="N16" s="10">
         <f>SUM(B16:M16)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -4622,7 +4703,7 @@
       </c>
       <c r="N17" s="10">
         <f>SUM(B17:M17)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -4669,7 +4750,7 @@
       </c>
       <c r="N18" s="10">
         <f>SUM(B18:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -4680,57 +4761,58 @@
       </c>
       <c r="B19" s="10">
         <f>SUM(B13:B18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="10">
         <f>SUM(C13:C18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>SUM(D13:D18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="10">
         <f>SUM(E13:E18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F19" s="10">
         <f>SUM(F13:F18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="10">
         <f>SUM(G13:G18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H19" s="10">
         <f>SUM(H13:H18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I19" s="10">
         <f>SUM(I13:I18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J19" s="10">
         <f>SUM(J13:J18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K19" s="10">
         <f>SUM(K13:K18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L19" s="10">
         <f>SUM(L13:L18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M19" s="10">
         <f>SUM(M13:M18)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N19" s="10">
         <f>SUM(N13:N18)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -4739,55 +4821,55 @@
       </c>
       <c r="B21" s="13">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="13">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="13">
         <f>D10-D19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="13">
         <f>E10-E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F21" s="13">
         <f>F10-F19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="13">
         <f>G10-G19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H21" s="13">
         <f>H10-H19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I21" s="13">
         <f>I10-I19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J21" s="13">
         <f>J10-J19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K21" s="13">
         <f>K10-K19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L21" s="13">
         <f>L10-L19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M21" s="13">
         <f>M10-M19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13">
         <f>N10-N19</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -4798,57 +4880,58 @@
       </c>
       <c r="B22" s="14">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="14">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D22" s="14">
         <f>IF(D10=0,0,D21/D10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="14">
         <f>IF(E10=0,0,E21/E10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F22" s="14">
         <f>IF(F10=0,0,F21/F10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="14">
         <f>IF(G10=0,0,G21/G10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H22" s="14">
         <f>IF(H10=0,0,H21/H10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I22" s="14">
         <f>IF(I10=0,0,I21/I10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J22" s="14">
         <f>IF(J10=0,0,J21/J10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K22" s="14">
         <f>IF(K10=0,0,K21/K10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L22" s="14">
         <f>IF(L10=0,0,L21/L10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M22" s="14">
         <f>IF(M10=0,0,M21/M10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N22" s="14">
         <f>IF(N10=0,0,N21/N10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -4862,7 +4945,16 @@
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4871,18 +4963,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="16"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
-    <col customWidth="1" max="7" min="7" width="18"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4899,6 +4991,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4959,7 +5052,7 @@
       </c>
       <c r="G5" s="17">
         <f>IF(B5=0,0,(F5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -5037,6 +5130,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
@@ -5050,6 +5146,15 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>